--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D05F73-E165-4E3D-ADAF-48CFA998B4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C903B171-8E26-42B0-997F-F3B25ADDC145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -262,6 +262,12 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>I had a low and unprodctive day because I was not well and I was sleeping the whole taking rest.</t>
   </si>
 </sst>
 </file>
@@ -1822,33 +1828,51 @@
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
         <v>46264</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
+      <c r="B22" s="14">
+        <v>650</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>0</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
+      </c>
       <c r="F22" s="14">
         <v>0</v>
       </c>
       <c r="G22" s="14">
         <v>0</v>
       </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="H22" s="14">
+        <v>0</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>650</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="18"/>
+        <v>790</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N22" s="18" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13">

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C903B171-8E26-42B0-997F-F3B25ADDC145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A338F6-10C8-4838-9F9D-114371FE1DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>I had a low and unprodctive day because I was not well and I was sleeping the whole taking rest.</t>
+  </si>
+  <si>
+    <t>Today I was kinda a feeling better and also cooked food and also also took proper rest and I am feeling good now.</t>
   </si>
 </sst>
 </file>
@@ -1874,33 +1877,51 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
         <v>46265</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
+      <c r="B23" s="14">
+        <v>550</v>
+      </c>
+      <c r="C23" s="14">
+        <v>30</v>
+      </c>
+      <c r="D23" s="14">
+        <v>0</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
+      </c>
       <c r="F23" s="14">
         <v>0</v>
       </c>
       <c r="G23" s="14">
         <v>0</v>
       </c>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="H23" s="14">
+        <v>200</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A338F6-10C8-4838-9F9D-114371FE1DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C92B1A71-4929-47D6-9228-AFC0C574CE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C92B1A71-4929-47D6-9228-AFC0C574CE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0AEF8CD-19F0-4A4E-B450-01D450C8A1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>Today I was kinda a feeling better and also cooked food and also also took proper rest and I am feeling good now.</t>
+  </si>
+  <si>
+    <t>Had a kinda good day and also feeling better it was a productive day from past 3 days.</t>
   </si>
 </sst>
 </file>
@@ -1923,27 +1926,51 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+    <row r="24" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B24" s="14">
+        <v>420</v>
+      </c>
+      <c r="C24" s="14">
+        <v>40</v>
+      </c>
+      <c r="D24" s="14">
+        <v>60</v>
+      </c>
+      <c r="E24" s="14">
+        <v>60</v>
+      </c>
+      <c r="F24" s="14">
+        <v>250</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>200</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0AEF8CD-19F0-4A4E-B450-01D450C8A1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5289C487-598F-44DB-8FAE-B0678A3185EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,9 @@
   <si>
     <t>Had a kinda good day and also feeling better it was a productive day from past 3 days.</t>
   </si>
+  <si>
+    <t>Today I was kinda a feeling low the whole day and also tierd .</t>
+  </si>
 </sst>
 </file>
 
@@ -283,7 +286,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -374,9 +377,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -437,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -484,14 +492,17 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -966,7 +977,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R401"/>
+  <dimension ref="A1:Y401"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -980,77 +991,77 @@
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-    </row>
-    <row r="2" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+    </row>
+    <row r="2" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="26">
         <v>12617413</v>
       </c>
-      <c r="G2" s="25"/>
-    </row>
-    <row r="3" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="26"/>
+    </row>
+    <row r="3" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="25"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+      <c r="G3" s="26"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A4" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-    </row>
-    <row r="5" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+    </row>
+    <row r="5" spans="1:25" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -1094,7 +1105,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>46223</v>
       </c>
@@ -1140,7 +1151,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" ht="63.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
         <v>46249</v>
       </c>
@@ -1182,11 +1193,11 @@
       <c r="M7" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="N7" s="22" t="s">
+      <c r="N7" s="23" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
         <v>46250</v>
       </c>
@@ -1228,7 +1239,7 @@
       <c r="M8" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="N8" s="20" t="s">
+      <c r="N8" s="21" t="s">
         <v>61</v>
       </c>
       <c r="O8" s="19"/>
@@ -1236,7 +1247,7 @@
       <c r="Q8" s="19"/>
       <c r="R8" s="19"/>
     </row>
-    <row r="9" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" ht="73.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
         <v>46251</v>
       </c>
@@ -1278,11 +1289,11 @@
       <c r="M9" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="N9" s="18" t="s">
+      <c r="N9" s="22" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="72" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <v>46252</v>
       </c>
@@ -1328,7 +1339,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="72" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" ht="88.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
         <v>46253</v>
       </c>
@@ -1374,7 +1385,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="72" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" ht="91.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
         <v>46254</v>
       </c>
@@ -1416,11 +1427,11 @@
       <c r="M12" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="N12" s="21" t="s">
+      <c r="N12" s="22" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="72" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
         <v>46255</v>
       </c>
@@ -1462,11 +1473,11 @@
       <c r="M13" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="N13" s="18" t="s">
+      <c r="N13" s="22" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
         <v>46256</v>
       </c>
@@ -1512,7 +1523,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" ht="78" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
         <v>46257</v>
       </c>
@@ -1554,11 +1565,19 @@
       <c r="M15" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="N15" t="s">
+      <c r="N15" s="22" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="20"/>
+      <c r="V15" s="20"/>
+    </row>
+    <row r="16" spans="1:25" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
         <v>46258</v>
       </c>
@@ -1600,11 +1619,22 @@
       <c r="M16" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N16" t="s">
+      <c r="N16" s="22" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O16" s="18"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="18"/>
+      <c r="R16" s="18"/>
+      <c r="S16" s="18"/>
+      <c r="T16" s="18"/>
+      <c r="U16" s="18"/>
+      <c r="V16" s="18"/>
+      <c r="W16" s="18"/>
+      <c r="X16" s="18"/>
+      <c r="Y16" s="18"/>
+    </row>
+    <row r="17" spans="1:25" ht="89.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
         <v>46259</v>
       </c>
@@ -1646,11 +1676,22 @@
       <c r="M17" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N17" t="s">
+      <c r="N17" s="22" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="O17" s="18"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="18"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="18"/>
+      <c r="T17" s="18"/>
+      <c r="U17" s="18"/>
+      <c r="V17" s="18"/>
+      <c r="W17" s="18"/>
+      <c r="X17" s="18"/>
+      <c r="Y17" s="18"/>
+    </row>
+    <row r="18" spans="1:25" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
         <v>46260</v>
       </c>
@@ -1692,11 +1733,11 @@
       <c r="M18" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="N18" s="21" t="s">
+      <c r="N18" s="22" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" ht="76.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
         <v>46261</v>
       </c>
@@ -1738,11 +1779,11 @@
       <c r="M19" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N19" s="18" t="s">
+      <c r="N19" s="22" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" ht="91.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
         <v>46262</v>
       </c>
@@ -1788,7 +1829,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" ht="85.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
         <v>46263</v>
       </c>
@@ -1830,11 +1871,11 @@
       <c r="M21" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="N21" s="21" t="s">
+      <c r="N21" s="22" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" ht="76.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
         <v>46264</v>
       </c>
@@ -1876,11 +1917,11 @@
       <c r="M22" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="N22" s="18" t="s">
+      <c r="N22" s="22" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
         <v>46265</v>
       </c>
@@ -1926,7 +1967,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
         <v>46266</v>
       </c>
@@ -1972,29 +2013,53 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+    <row r="25" spans="1:25" ht="82.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B25" s="14">
+        <v>450</v>
+      </c>
+      <c r="C25" s="14">
+        <v>50</v>
+      </c>
+      <c r="D25" s="14">
+        <v>60</v>
+      </c>
+      <c r="E25" s="14">
+        <v>50</v>
+      </c>
+      <c r="F25" s="14">
+        <v>250</v>
+      </c>
+      <c r="G25" s="14">
+        <v>5</v>
+      </c>
+      <c r="H25" s="14">
+        <v>250</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -2016,7 +2081,7 @@
       <c r="M26" s="16"/>
       <c r="N26" s="17"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
@@ -2038,7 +2103,7 @@
       <c r="M27" s="16"/>
       <c r="N27" s="17"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" ht="93" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -2060,7 +2125,7 @@
       <c r="M28" s="16"/>
       <c r="N28" s="17"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -2082,7 +2147,7 @@
       <c r="M29" s="16"/>
       <c r="N29" s="17"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
@@ -2104,7 +2169,7 @@
       <c r="M30" s="16"/>
       <c r="N30" s="17"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" ht="102.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
@@ -2126,7 +2191,7 @@
       <c r="M31" s="16"/>
       <c r="N31" s="17"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -2148,7 +2213,7 @@
       <c r="M32" s="16"/>
       <c r="N32" s="17"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -2170,7 +2235,7 @@
       <c r="M33" s="16"/>
       <c r="N33" s="17"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="116.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
@@ -2192,7 +2257,7 @@
       <c r="M34" s="16"/>
       <c r="N34" s="17"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
@@ -2214,7 +2279,7 @@
       <c r="M35" s="16"/>
       <c r="N35" s="17"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5289C487-598F-44DB-8FAE-B0678A3185EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5084C400-5ABB-49E3-B75A-FE9B6312D0F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -277,6 +277,9 @@
   </si>
   <si>
     <t>Today I was kinda a feeling low the whole day and also tierd .</t>
+  </si>
+  <si>
+    <t>Had a very good day and it was also productive . The energy level was high and enjoyed the day .</t>
   </si>
 </sst>
 </file>
@@ -2060,26 +2063,50 @@
       </c>
     </row>
     <row r="26" spans="1:25" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B26" s="14">
+        <v>430</v>
+      </c>
+      <c r="C26" s="14">
+        <v>50</v>
+      </c>
+      <c r="D26" s="14">
+        <v>60</v>
+      </c>
+      <c r="E26" s="14">
+        <v>30</v>
+      </c>
+      <c r="F26" s="14">
+        <v>300</v>
+      </c>
+      <c r="G26" s="14">
+        <v>6</v>
+      </c>
+      <c r="H26" s="14">
+        <v>250</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="27" spans="1:25" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>

--- a/12617413.xlsx
+++ b/12617413.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academic\MCA\SEM-1\CAP-776(PY)\EXCEL SHEET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5084C400-5ABB-49E3-B75A-FE9B6312D0F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696BE575-E26B-49FF-9591-9177886705BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>Had a very good day and it was also productive . The energy level was high and enjoyed the day .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Had a very good and productive day and the level of energy was also kinda good but the was also very tiering </t>
   </si>
 </sst>
 </file>
@@ -2109,26 +2112,50 @@
       </c>
     </row>
     <row r="27" spans="1:25" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B27" s="14">
+        <v>410</v>
+      </c>
+      <c r="C27" s="14">
+        <v>60</v>
+      </c>
+      <c r="D27" s="14">
+        <v>60</v>
+      </c>
+      <c r="E27" s="14">
+        <v>50</v>
+      </c>
+      <c r="F27" s="14">
+        <v>350</v>
+      </c>
+      <c r="G27" s="14">
+        <v>7</v>
+      </c>
+      <c r="H27" s="14">
+        <v>300</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="28" spans="1:25" ht="93" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
